--- a/Bar Charts for ppt.xlsx
+++ b/Bar Charts for ppt.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="126" documentId="8_{F7079509-7F89-4B1F-A474-FAD18052C559}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA587399-0722-4DDD-AD03-DB441D96D9A3}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="4240" yWindow="4280" windowWidth="19200" windowHeight="11180" xr2:uid="{3449709D-A89B-448E-AB81-287460E0A640}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{3449709D-A89B-448E-AB81-287460E0A640}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
